--- a/public/downloads/JiangDynamic2023.xlsx
+++ b/public/downloads/JiangDynamic2023.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -656,10 +679,10 @@
         <v>133</v>
       </c>
       <c r="N3" s="5">
-        <v>734.4871456623077</v>
+        <v>734487.1456623077</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03511436370714289</v>
+        <v>35.11436370714289</v>
       </c>
       <c r="P3" s="5">
         <v>20917</v>
@@ -706,10 +729,10 @@
         <v>133</v>
       </c>
       <c r="N4" s="5">
-        <v>1162.243246555328</v>
+        <v>1162243.246555328</v>
       </c>
       <c r="O4" s="4">
-        <v>0.07727167386179964</v>
+        <v>77.27167386179964</v>
       </c>
       <c r="P4" s="5">
         <v>15041</v>
@@ -756,10 +779,10 @@
         <v>133</v>
       </c>
       <c r="N5" s="5">
-        <v>2550.40102148056</v>
+        <v>2550401.02148056</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1371994739620507</v>
+        <v>137.1994739620507</v>
       </c>
       <c r="P5" s="5">
         <v>18589</v>
@@ -806,10 +829,10 @@
         <v>133</v>
       </c>
       <c r="N6" s="5">
-        <v>1302.171833753586</v>
+        <v>1302171.833753586</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08983593195954369</v>
+        <v>89.83593195954369</v>
       </c>
       <c r="P6" s="5">
         <v>14495</v>
@@ -856,10 +879,10 @@
         <v>133</v>
       </c>
       <c r="N7" s="5">
-        <v>4059.760851860046</v>
+        <v>4059760.851860046</v>
       </c>
       <c r="O7" s="4">
-        <v>0.3479695596005868</v>
+        <v>347.9695596005868</v>
       </c>
       <c r="P7" s="5">
         <v>11667</v>
@@ -906,10 +929,10 @@
         <v>133</v>
       </c>
       <c r="N8" s="5">
-        <v>360.7150123119354</v>
+        <v>360715.0123119354</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02492502849032168</v>
+        <v>24.92502849032168</v>
       </c>
       <c r="P8" s="5">
         <v>14472</v>
@@ -956,10 +979,10 @@
         <v>133</v>
       </c>
       <c r="N9" s="5">
-        <v>554.1453802585602</v>
+        <v>554145.3802585602</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03652421435925127</v>
+        <v>36.52421435925127</v>
       </c>
       <c r="P9" s="5">
         <v>15172</v>
@@ -1006,10 +1029,10 @@
         <v>133</v>
       </c>
       <c r="N10" s="5">
-        <v>1215.529389858246</v>
+        <v>1215529.389858246</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08391063025391729</v>
+        <v>83.91063025391729</v>
       </c>
       <c r="P10" s="5">
         <v>14486</v>
@@ -1056,10 +1079,10 @@
         <v>133</v>
       </c>
       <c r="N11" s="5">
-        <v>733.8017089366913</v>
+        <v>733801.7089366913</v>
       </c>
       <c r="O11" s="4">
-        <v>0.0537111483631014</v>
+        <v>53.71114836310139</v>
       </c>
       <c r="P11" s="5">
         <v>13662</v>
@@ -1106,10 +1129,10 @@
         <v>133</v>
       </c>
       <c r="N12" s="5">
-        <v>338.2368311882019</v>
+        <v>338236.8311882019</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0257449254976558</v>
+        <v>25.7449254976558</v>
       </c>
       <c r="P12" s="5">
         <v>13138</v>
@@ -1156,10 +1179,10 @@
         <v>133</v>
       </c>
       <c r="N13" s="5">
-        <v>1594.343828201294</v>
+        <v>1594343.828201294</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07643067249287123</v>
+        <v>76.43067249287124</v>
       </c>
       <c r="P13" s="5">
         <v>20860</v>
@@ -1206,10 +1229,10 @@
         <v>110</v>
       </c>
       <c r="N14" s="5">
-        <v>11749.53292417526</v>
+        <v>11749532.92417526</v>
       </c>
       <c r="O14" s="4">
-        <v>0.4572692323088252</v>
+        <v>457.2692323088252</v>
       </c>
       <c r="P14" s="5">
         <v>25695</v>
@@ -1256,10 +1279,10 @@
         <v>110</v>
       </c>
       <c r="N15" s="5">
-        <v>4816.135705947876</v>
+        <v>4816135.705947876</v>
       </c>
       <c r="O15" s="4">
-        <v>0.4861836973498764</v>
+        <v>486.1836973498764</v>
       </c>
       <c r="P15" s="5">
         <v>9906</v>
@@ -1306,10 +1329,10 @@
         <v>110</v>
       </c>
       <c r="N16" s="5">
-        <v>6189.23518037796</v>
+        <v>6189235.18037796</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1075005242015139</v>
+        <v>107.5005242015139</v>
       </c>
       <c r="P16" s="5">
         <v>57574</v>
@@ -1356,10 +1379,10 @@
         <v>110</v>
       </c>
       <c r="N17" s="5">
-        <v>1332.343561649323</v>
+        <v>1332343.561649323</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1062220809733973</v>
+        <v>106.2220809733973</v>
       </c>
       <c r="P17" s="5">
         <v>12543</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,91 +1494,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4731187577596403</v>
+        <v>0.6148791019942604</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4367254669671196</v>
+        <v>0.577355914817737</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2654986984748964</v>
+        <v>0.4788960767495722</v>
       </c>
       <c r="E3" s="4">
-        <v>91.59224085673874</v>
+        <v>91.99535259648414</v>
       </c>
       <c r="F3" s="4">
-        <v>87.59563204642609</v>
+        <v>85.69539504286</v>
       </c>
       <c r="G3" s="5">
         <v>101</v>
       </c>
       <c r="H3" s="5">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.09641456870488674</v>
+      </c>
+      <c r="O3" s="5">
+        <v>90</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6239493167297497</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5864634383686206</v>
+      </c>
+      <c r="R3" s="5">
+        <v>90</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1194290257289797</v>
+        <v>0.308850881708218</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1060580214822693</v>
+        <v>0.25612791588037</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1123747386406977</v>
+        <v>0.2088225107407753</v>
       </c>
       <c r="E4" s="4">
-        <v>87.06349206349206</v>
+        <v>85.02267573696145</v>
       </c>
       <c r="F4" s="4">
-        <v>81.42803877703233</v>
+        <v>72.9791200596552</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.25612791588037</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2133333703906525</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1885135138791156</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1643,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1662,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1704,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,75 +1735,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4580589350230466</v>
+        <v>0.741428937323835</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4243707022068831</v>
+        <v>0.7693647884662267</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3466452378479866</v>
+        <v>0.5105723521402656</v>
       </c>
       <c r="E3" s="4">
-        <v>92.54361150400753</v>
+        <v>91.13996093486899</v>
       </c>
       <c r="F3" s="4">
-        <v>87.32429618800762</v>
+        <v>83.26278601014486</v>
       </c>
       <c r="G3" s="5">
         <v>101</v>
       </c>
       <c r="H3" s="5">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0495352906921368</v>
+      </c>
+      <c r="O3" s="5">
+        <v>87</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7508858906588549</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.77806606575437</v>
+      </c>
+      <c r="R3" s="5">
+        <v>87</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3001871575873136</v>
+        <v>0.3280220717887106</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2944257444558908</v>
+        <v>0.3489723955078148</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2331368210877574</v>
+        <v>0.2812371410297045</v>
       </c>
       <c r="E4" s="4">
-        <v>86.48148148148147</v>
+        <v>83.71882086167803</v>
       </c>
       <c r="F4" s="4">
-        <v>78.13447675863563</v>
+        <v>69.9428287347731</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
         <v>1</v>
@@ -1711,9 +1853,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3280220717887106</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3489723955078148</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1882,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1890,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1901,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1943,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,75 +1974,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3197065490360623</v>
+        <v>0.4731187577596403</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2679205097228394</v>
+        <v>0.4367254669671196</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3083719191871006</v>
+        <v>0.2654986984748964</v>
       </c>
       <c r="E3" s="4">
-        <v>94.15201724254059</v>
+        <v>91.59224085673874</v>
       </c>
       <c r="F3" s="4">
-        <v>89.26551044366109</v>
+        <v>87.59563204642609</v>
       </c>
       <c r="G3" s="5">
         <v>101</v>
       </c>
       <c r="H3" s="5">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2804145229426144</v>
+      </c>
+      <c r="O3" s="5">
+        <v>89</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4618062706812343</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4240305105108392</v>
+      </c>
+      <c r="R3" s="5">
+        <v>89</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1710729118115321</v>
+        <v>0.1194290257289797</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1541955622858658</v>
+        <v>0.1060580214822693</v>
       </c>
       <c r="D4" s="4">
-        <v>0.148922264022076</v>
+        <v>0.1123747386406977</v>
       </c>
       <c r="E4" s="4">
-        <v>87.61148904006046</v>
+        <v>87.06349206349206</v>
       </c>
       <c r="F4" s="4">
-        <v>78.0350484712901</v>
+        <v>81.42803877703233</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>1</v>
@@ -1883,9 +2092,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.002603129700034401</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1197182623623168</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1067088039072779</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2123,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2142,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2184,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,66 +2215,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4809624348385427</v>
+        <v>0.4580589350230466</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4490255755926643</v>
+        <v>0.4243707022068831</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2332218253726771</v>
+        <v>0.3466452378479866</v>
       </c>
       <c r="E3" s="4">
-        <v>92.92079207920793</v>
+        <v>92.54361150400753</v>
       </c>
       <c r="F3" s="4">
-        <v>88.96216802888468</v>
+        <v>87.32429618800762</v>
       </c>
       <c r="G3" s="5">
         <v>101</v>
       </c>
       <c r="H3" s="5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.02145297005440796</v>
+      </c>
+      <c r="O3" s="5">
+        <v>93</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4576975298520651</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4244395626137615</v>
+      </c>
+      <c r="R3" s="5">
+        <v>93</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2857564378231119</v>
+        <v>0.3001871575873136</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2525062422311391</v>
+        <v>0.2944257444558908</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2833430060197265</v>
+        <v>0.2331368210877574</v>
       </c>
       <c r="E4" s="4">
-        <v>87.09372637944064</v>
+        <v>86.48148148148147</v>
       </c>
       <c r="F4" s="4">
-        <v>78.09967685806653</v>
+        <v>78.13447675863563</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -2055,9 +2333,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.1408404613225035</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.273448582497741</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2600475764835832</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2364,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2372,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2383,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2425,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,91 +2456,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.824797126167641</v>
+        <v>0.3197065490360623</v>
       </c>
       <c r="C3" s="4">
-        <v>0.9897455102705498</v>
+        <v>0.2679205097228394</v>
       </c>
       <c r="D3" s="4">
-        <v>1.0878912023358</v>
+        <v>0.3083719191871006</v>
       </c>
       <c r="E3" s="4">
-        <v>77.49376978514178</v>
+        <v>94.15201724254059</v>
       </c>
       <c r="F3" s="4">
-        <v>66.71650386515245</v>
+        <v>89.26551044366109</v>
       </c>
       <c r="G3" s="5">
         <v>101</v>
       </c>
       <c r="H3" s="5">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1731566757425481</v>
+      </c>
+      <c r="O3" s="5">
+        <v>92</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3008560352081979</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2559832763496457</v>
+      </c>
+      <c r="R3" s="5">
+        <v>92</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6234659260187022</v>
+        <v>0.1710729118115321</v>
       </c>
       <c r="C4" s="4">
-        <v>0.124554305474021</v>
+        <v>0.1541955622858658</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3585984259481797</v>
+        <v>0.148922264022076</v>
       </c>
       <c r="E4" s="4">
-        <v>69.96598639455785</v>
+        <v>87.61148904006046</v>
       </c>
       <c r="F4" s="4">
-        <v>42.89709172259526</v>
+        <v>78.0350484712901</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
+        <v>7</v>
+      </c>
+      <c r="I4" s="5">
         <v>1</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
       <c r="J4" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.06516114618796109</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1434413483784359</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1372867367827309</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,34 +2697,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8534041405520787</v>
+        <v>0.4809624348385427</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8566518384203367</v>
+        <v>0.4490255755926643</v>
       </c>
       <c r="D3" s="4">
-        <v>1.186111021519785</v>
+        <v>0.2332218253726771</v>
       </c>
       <c r="E3" s="4">
-        <v>94.19680743584563</v>
+        <v>92.92079207920793</v>
       </c>
       <c r="F3" s="4">
-        <v>90.01306842093582</v>
+        <v>88.96216802888468</v>
       </c>
       <c r="G3" s="5">
         <v>101</v>
       </c>
       <c r="H3" s="5">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
         <v>7</v>
@@ -2358,25 +2756,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2588246301165238</v>
+      </c>
+      <c r="O3" s="5">
+        <v>92</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4678102639766296</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.431773468123428</v>
+      </c>
+      <c r="R3" s="5">
+        <v>92</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1432275625824862</v>
+        <v>0.2857564378231119</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1046511971567432</v>
+        <v>0.2525062422311391</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1630771196865276</v>
+        <v>0.2833430060197265</v>
       </c>
       <c r="E4" s="4">
-        <v>84.61451247165574</v>
+        <v>87.09372637944064</v>
       </c>
       <c r="F4" s="4">
-        <v>77.34899328858837</v>
+        <v>78.09967685806653</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -2385,23 +2801,41 @@
         <v>7</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.2525062422311391</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1566734708037186</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1586870681293875</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2846,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2854,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2865,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2907,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,66 +2938,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>2.54310489458399</v>
+        <v>1.824797126167641</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.9897455102705498</v>
       </c>
       <c r="D3" s="4">
-        <v>1.962051339840142</v>
+        <v>1.0878912023358</v>
       </c>
       <c r="E3" s="4">
-        <v>62.72007813026202</v>
+        <v>77.49376978514178</v>
       </c>
       <c r="F3" s="4">
-        <v>36.95616541519924</v>
+        <v>66.71650386515245</v>
       </c>
       <c r="G3" s="5">
         <v>101</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="K3" s="5">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>17</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.581612773675094</v>
+      </c>
+      <c r="O3" s="5">
+        <v>47</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.190499194664065</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.9333839077604529</v>
+      </c>
+      <c r="R3" s="5">
+        <v>42</v>
+      </c>
+      <c r="S3" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2826372226857959</v>
+        <v>0.6234659260187022</v>
       </c>
       <c r="C4" s="4">
-        <v>0.07430240591520487</v>
+        <v>0.124554305474021</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3165944403367702</v>
+        <v>0.3585984259481797</v>
       </c>
       <c r="E4" s="4">
-        <v>64.90929705215443</v>
+        <v>69.96598639455785</v>
       </c>
       <c r="F4" s="4">
-        <v>39.92791449167274</v>
+        <v>42.89709172259526</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -2571,9 +3056,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6234659260187022</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.124554305474021</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3085,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3093,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3104,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3146,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,66 +3177,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.456067316804817</v>
+        <v>0.8534041405520787</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4317193309536364</v>
+        <v>0.8566518384203367</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6867571504753105</v>
+        <v>1.186111021519785</v>
       </c>
       <c r="E3" s="4">
-        <v>93.28820637165758</v>
+        <v>94.19680743584563</v>
       </c>
       <c r="F3" s="4">
-        <v>88.88231776197635</v>
+        <v>90.01306842093582</v>
       </c>
       <c r="G3" s="5">
         <v>101</v>
       </c>
       <c r="H3" s="5">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.8566518384203367</v>
+      </c>
+      <c r="O3" s="5">
+        <v>94</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2190812034743391</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2271993236472406</v>
+      </c>
+      <c r="R3" s="5">
+        <v>94</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1514568702953183</v>
+        <v>0.1432275625824862</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1542655943087863</v>
+        <v>0.1046511971567432</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1446298149210053</v>
+        <v>0.1630771196865276</v>
       </c>
       <c r="E4" s="4">
-        <v>84.57671957671998</v>
+        <v>84.61451247165574</v>
       </c>
       <c r="F4" s="4">
-        <v>79.2020879940321</v>
+        <v>77.34899328858837</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -2743,9 +3295,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.07904438335567322</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1426137115841984</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1038619601589447</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3326,1344 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2.54310489458399</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>1.962051339840142</v>
+      </c>
+      <c r="E3" s="4">
+        <v>62.72007813026202</v>
+      </c>
+      <c r="F3" s="4">
+        <v>36.95616541519924</v>
+      </c>
+      <c r="G3" s="5">
+        <v>101</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>101</v>
+      </c>
+      <c r="K3" s="5">
+        <v>19</v>
+      </c>
+      <c r="L3" s="5">
+        <v>79</v>
+      </c>
+      <c r="M3" s="5">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.54310489458399</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2826372226857959</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.07430240591520487</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3165944403367702</v>
+      </c>
+      <c r="E4" s="4">
+        <v>64.90929705215443</v>
+      </c>
+      <c r="F4" s="4">
+        <v>39.92791449167274</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>8</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2826372226857959</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07430240591520487</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.456067316804817</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4317193309536364</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6867571504753105</v>
+      </c>
+      <c r="E3" s="4">
+        <v>93.28820637165758</v>
+      </c>
+      <c r="F3" s="4">
+        <v>88.88231776197635</v>
+      </c>
+      <c r="G3" s="5">
+        <v>101</v>
+      </c>
+      <c r="H3" s="5">
+        <v>90</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3343484532302963</v>
+      </c>
+      <c r="O3" s="5">
+        <v>90</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.339901245954752</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3142222757335684</v>
+      </c>
+      <c r="R3" s="5">
+        <v>90</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1514568702953183</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1542655943087863</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1446298149210053</v>
+      </c>
+      <c r="E4" s="4">
+        <v>84.57671957671998</v>
+      </c>
+      <c r="F4" s="4">
+        <v>79.2020879940321</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>7</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.06280850348866807</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1386856787222541</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1557907775687519</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>87.96992481203007</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2.255639097744361</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9.774436090225564</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2.255639097744361</v>
+      </c>
+      <c r="F3" s="3">
+        <v>7.518796992481203</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4042101802733519</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3833863798958821</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3729603204355827</v>
+      </c>
+      <c r="K3" s="4">
+        <v>90.79535573627912</v>
+      </c>
+      <c r="L3" s="4">
+        <v>85.95347428975016</v>
+      </c>
+      <c r="M3" s="5">
+        <v>133</v>
+      </c>
+      <c r="N3" s="5">
+        <v>734487.1456623077</v>
+      </c>
+      <c r="O3" s="4">
+        <v>35.11436370714289</v>
+      </c>
+      <c r="P3" s="5">
+        <v>20917</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>88.72180451127819</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4.511278195488721</v>
+      </c>
+      <c r="D4" s="3">
+        <v>6.766917293233083</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3.759398496240602</v>
+      </c>
+      <c r="G4" s="3">
+        <v>3.007518796992481</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.749943831956182</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.6989533938624787</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.5427157389213658</v>
+      </c>
+      <c r="K4" s="4">
+        <v>90.80865428878319</v>
+      </c>
+      <c r="L4" s="4">
+        <v>83.53677818707612</v>
+      </c>
+      <c r="M4" s="5">
+        <v>133</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1162243.246555328</v>
+      </c>
+      <c r="O4" s="4">
+        <v>77.27167386179964</v>
+      </c>
+      <c r="P4" s="5">
+        <v>15041</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>93.23308270676691</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.7518796992481203</v>
+      </c>
+      <c r="D5" s="3">
+        <v>6.015037593984962</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.503759398496241</v>
+      </c>
+      <c r="F5" s="3">
+        <v>4.511278195488721</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.3127307007823732</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2957289045704428</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.3093916503042597</v>
+      </c>
+      <c r="K5" s="4">
+        <v>91.27103472968135</v>
+      </c>
+      <c r="L5" s="4">
+        <v>87.82257657566836</v>
+      </c>
+      <c r="M5" s="5">
+        <v>133</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2550401.02148056</v>
+      </c>
+      <c r="O5" s="4">
+        <v>137.1994739620507</v>
+      </c>
+      <c r="P5" s="5">
+        <v>18589</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>84.21052631578947</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.255639097744361</v>
+      </c>
+      <c r="D6" s="3">
+        <v>13.53383458646617</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>13.53383458646617</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4681317802741446</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.4592244801517469</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.3863580490467429</v>
+      </c>
+      <c r="K6" s="4">
+        <v>90.59485448314666</v>
+      </c>
+      <c r="L6" s="4">
+        <v>85.13969487477132</v>
+      </c>
+      <c r="M6" s="5">
+        <v>133</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1302171.833753586</v>
+      </c>
+      <c r="O6" s="4">
+        <v>89.83593195954369</v>
+      </c>
+      <c r="P6" s="5">
+        <v>14495</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>91.72932330827066</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.503759398496241</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6.766917293233083</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1.503759398496241</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2943241539491034</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2368639299572834</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.4012331824952504</v>
+      </c>
+      <c r="K7" s="4">
+        <v>93.46324996163848</v>
+      </c>
+      <c r="L7" s="4">
+        <v>89.13214243662691</v>
+      </c>
+      <c r="M7" s="5">
+        <v>133</v>
+      </c>
+      <c r="N7" s="5">
+        <v>4059760.851860046</v>
+      </c>
+      <c r="O7" s="4">
+        <v>347.9695596005868</v>
+      </c>
+      <c r="P7" s="5">
+        <v>11667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>87.96992481203007</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2.255639097744361</v>
+      </c>
+      <c r="D8" s="3">
+        <v>9.774436090225564</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>9.774436090225564</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.6065001410258234</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.5760590307522571</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.4290191597718513</v>
+      </c>
+      <c r="K8" s="4">
+        <v>91.15083627435936</v>
+      </c>
+      <c r="L8" s="4">
+        <v>84.59479235000128</v>
+      </c>
+      <c r="M8" s="5">
+        <v>133</v>
+      </c>
+      <c r="N8" s="5">
+        <v>360715.0123119354</v>
+      </c>
+      <c r="O8" s="4">
+        <v>24.92502849032168</v>
+      </c>
+      <c r="P8" s="5">
+        <v>14472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>81.95488721804512</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4.511278195488721</v>
+      </c>
+      <c r="D9" s="3">
+        <v>13.53383458646617</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>13.53383458646617</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.7297493373032723</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.7644717432827777</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4876513561060258</v>
+      </c>
+      <c r="K9" s="4">
+        <v>90.20663904659611</v>
+      </c>
+      <c r="L9" s="4">
+        <v>81.81981800137805</v>
+      </c>
+      <c r="M9" s="5">
+        <v>133</v>
+      </c>
+      <c r="N9" s="5">
+        <v>554145.3802585602</v>
+      </c>
+      <c r="O9" s="4">
+        <v>36.52421435925127</v>
+      </c>
+      <c r="P9" s="5">
+        <v>15172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>87.96992481203007</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.255639097744361</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9.774436090225564</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.503759398496241</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8.270676691729323</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.4068171247342299</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3775117915952573</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3716209371465818</v>
+      </c>
+      <c r="K10" s="4">
+        <v>91.04700526827273</v>
+      </c>
+      <c r="L10" s="4">
+        <v>86.89038031319869</v>
+      </c>
+      <c r="M10" s="5">
+        <v>133</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1215529.389858246</v>
+      </c>
+      <c r="O10" s="4">
+        <v>83.91063025391729</v>
+      </c>
+      <c r="P10" s="5">
+        <v>14486</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>91.72932330827066</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.255639097744361</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6.015037593984962</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>6.015037593984962</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.4542013147619492</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.4274139239694594</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.3536619496173149</v>
+      </c>
+      <c r="K11" s="4">
+        <v>91.87765331696588</v>
+      </c>
+      <c r="L11" s="4">
+        <v>86.5956838404725</v>
+      </c>
+      <c r="M11" s="5">
+        <v>133</v>
+      </c>
+      <c r="N11" s="5">
+        <v>733801.7089366913</v>
+      </c>
+      <c r="O11" s="4">
+        <v>53.71114836310139</v>
+      </c>
+      <c r="P11" s="5">
+        <v>13662</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>91.72932330827066</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.255639097744361</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6.015037593984962</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>6.015037593984962</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2810251674914412</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2476260997260189</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.3450093379721784</v>
+      </c>
+      <c r="K12" s="4">
+        <v>93.56963838166847</v>
+      </c>
+      <c r="L12" s="4">
+        <v>88.73837277758138</v>
+      </c>
+      <c r="M12" s="5">
+        <v>133</v>
+      </c>
+      <c r="N12" s="5">
+        <v>338236.8311882019</v>
+      </c>
+      <c r="O12" s="4">
+        <v>25.7449254976558</v>
+      </c>
+      <c r="P12" s="5">
+        <v>13138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>90.22556390977444</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.255639097744361</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7.518796992481203</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.7518796992481203</v>
+      </c>
+      <c r="F13" s="3">
+        <v>6.766917293233083</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.4170568556693248</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.3890062357698064</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.3622978995901615</v>
+      </c>
+      <c r="K13" s="4">
+        <v>92.25180297682985</v>
+      </c>
+      <c r="L13" s="4">
+        <v>87.94788985887492</v>
+      </c>
+      <c r="M13" s="5">
+        <v>133</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1594343.828201294</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.43067249287124</v>
+      </c>
+      <c r="P13" s="5">
+        <v>20860</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>39.09090909090909</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>60.90909090909091</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="F14" s="3">
+        <v>51.81818181818182</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1.144105563593081</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.9145739170096057</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.856047107888858</v>
+      </c>
+      <c r="K14" s="4">
+        <v>76.87786023500307</v>
+      </c>
+      <c r="L14" s="4">
+        <v>64.76764287166945</v>
+      </c>
+      <c r="M14" s="5">
+        <v>110</v>
+      </c>
+      <c r="N14" s="5">
+        <v>11749532.92417526</v>
+      </c>
+      <c r="O14" s="4">
+        <v>457.2692323088252</v>
+      </c>
+      <c r="P14" s="5">
+        <v>25695</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>91.81818181818183</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.181818181818182</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>8.181818181818182</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2128247723196913</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2186511895440913</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.3949315992231434</v>
+      </c>
+      <c r="K15" s="4">
+        <v>93.41280148423051</v>
+      </c>
+      <c r="L15" s="4">
+        <v>88.97691681919727</v>
+      </c>
+      <c r="M15" s="5">
+        <v>110</v>
+      </c>
+      <c r="N15" s="5">
+        <v>4816135.705947876</v>
+      </c>
+      <c r="O15" s="4">
+        <v>486.1836973498764</v>
+      </c>
+      <c r="P15" s="5">
+        <v>9906</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>99.09090909090909</v>
+      </c>
+      <c r="E16" s="3">
+        <v>17.27272727272727</v>
+      </c>
+      <c r="F16" s="3">
+        <v>79.09090909090909</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2.727272727272727</v>
+      </c>
+      <c r="H16" s="4">
+        <v>2.358157539610501</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.07430240591520487</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1.827423048062594</v>
+      </c>
+      <c r="K16" s="4">
+        <v>62.89919604205316</v>
+      </c>
+      <c r="L16" s="4">
+        <v>37.19930852145597</v>
+      </c>
+      <c r="M16" s="5">
+        <v>110</v>
+      </c>
+      <c r="N16" s="5">
+        <v>6189235.18037796</v>
+      </c>
+      <c r="O16" s="4">
+        <v>107.5005242015139</v>
+      </c>
+      <c r="P16" s="5">
+        <v>57574</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>88.18181818181819</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.818181818181818</v>
+      </c>
+      <c r="D17" s="3">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>10</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.3234381540902749</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.3027890748350765</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.3492609618536484</v>
+      </c>
+      <c r="K17" s="4">
+        <v>92.5754483611631</v>
+      </c>
+      <c r="L17" s="4">
+        <v>88.09029896278173</v>
+      </c>
+      <c r="M17" s="5">
+        <v>110</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1332343.561649323</v>
+      </c>
+      <c r="O17" s="4">
+        <v>106.2220809733973</v>
+      </c>
+      <c r="P17" s="5">
+        <v>12543</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2875,16 +4777,16 @@
         <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>3</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -2963,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
         <v>2</v>
@@ -3321,10 +5223,10 @@
         <v>2</v>
       </c>
       <c r="M13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3362,13 +5264,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3450,13 +5352,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="M16" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>87</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3516,9 +5418,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>117</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>118</v>
+      </c>
+      <c r="C4" s="5">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>5</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>124</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>112</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>18</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>18</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>122</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>7</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>117</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>13</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>109</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>18</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>8</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>117</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>13</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2</v>
+      </c>
+      <c r="F10" s="5">
+        <v>11</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5">
+        <v>2</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>5</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>122</v>
+      </c>
+      <c r="C11" s="5">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>8</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>122</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>8</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>120</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>10</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
+        <v>9</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>43</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>67</v>
+      </c>
+      <c r="E14" s="5">
+        <v>5</v>
+      </c>
+      <c r="F14" s="5">
+        <v>57</v>
+      </c>
+      <c r="G14" s="5">
+        <v>5</v>
+      </c>
+      <c r="H14" s="5">
+        <v>5</v>
+      </c>
+      <c r="I14" s="5">
+        <v>4</v>
+      </c>
+      <c r="J14" s="5">
+        <v>3</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>28</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>101</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>9</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>109</v>
+      </c>
+      <c r="E16" s="5">
+        <v>19</v>
+      </c>
+      <c r="F16" s="5">
+        <v>87</v>
+      </c>
+      <c r="G16" s="5">
+        <v>3</v>
+      </c>
+      <c r="H16" s="5">
+        <v>19</v>
+      </c>
+      <c r="I16" s="5">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5">
+        <v>12</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>77</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>97</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
+        <v>11</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>4</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6186,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6228,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,10 +6259,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4366825867300003</v>
@@ -3629,10 +6318,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.08247222784529971</v>
+      </c>
+      <c r="O3" s="5">
+        <v>92</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4335050162872681</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4191752189883338</v>
+      </c>
+      <c r="R3" s="5">
+        <v>92</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6981273315134331</v>
@@ -3670,9 +6377,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.7249473826592066</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1228267362154257</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1018654030620746</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6408,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6427,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6469,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,10 +6500,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.8291106159054769</v>
@@ -3801,10 +6559,28 @@
       <c r="M3" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.08358244615315355</v>
+      </c>
+      <c r="O3" s="5">
+        <v>94</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8315361465461627</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7547966148785786</v>
+      </c>
+      <c r="R3" s="5">
+        <v>90</v>
+      </c>
+      <c r="S3" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2354756344965254</v>
@@ -3842,9 +6618,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.1034192243750264</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2369869917534844</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2419385551562654</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6649,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6668,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6710,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,10 +6741,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3693121485451866</v>
@@ -3973,10 +6800,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2864326960377471</v>
+      </c>
+      <c r="O3" s="5">
+        <v>95</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3299861176413893</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.309983392113737</v>
+      </c>
+      <c r="R3" s="5">
+        <v>95</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2349306213536188</v>
@@ -4014,9 +6859,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.1520537010616831</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2484736946983138</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2493712994703494</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6890,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6909,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6951,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,10 +6982,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5113681922393981</v>
@@ -4145,10 +7041,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.0752868972970023</v>
+      </c>
+      <c r="O3" s="5">
+        <v>88</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4998817478323011</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4880947693974953</v>
+      </c>
+      <c r="R3" s="5">
+        <v>88</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.314501068874506</v>
@@ -4186,9 +7100,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.02873115386428253</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3176934193038707</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2727969549847694</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7131,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7150,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7192,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,10 +7223,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2857360317310712</v>
@@ -4317,10 +7282,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.08040037005859409</v>
+      </c>
+      <c r="O3" s="5">
+        <v>94</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2737612898095583</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.24308175578526</v>
+      </c>
+      <c r="R3" s="5">
+        <v>94</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1528326077554993</v>
@@ -4358,9 +7341,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.09018686809444887</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.133287598753916</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1250064900930603</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7372,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6148791019942604</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.577355914817737</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4788960767495722</v>
-      </c>
-      <c r="E3" s="4">
-        <v>91.99535259648414</v>
-      </c>
-      <c r="F3" s="4">
-        <v>85.69539504286</v>
-      </c>
-      <c r="G3" s="5">
-        <v>101</v>
-      </c>
-      <c r="H3" s="5">
-        <v>90</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>9</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>9</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.308850881708218</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.25612791588037</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2088225107407753</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.02267573696145</v>
-      </c>
-      <c r="F4" s="4">
-        <v>72.9791200596552</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>6</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.741428937323835</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7693647884662267</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5105723521402656</v>
-      </c>
-      <c r="E3" s="4">
-        <v>91.13996093486899</v>
-      </c>
-      <c r="F3" s="4">
-        <v>83.26278601014486</v>
-      </c>
-      <c r="G3" s="5">
-        <v>101</v>
-      </c>
-      <c r="H3" s="5">
-        <v>87</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>12</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>12</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3280220717887106</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3489723955078148</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2812371410297045</v>
-      </c>
-      <c r="E4" s="4">
-        <v>83.71882086167803</v>
-      </c>
-      <c r="F4" s="4">
-        <v>69.9428287347731</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>4</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/JiangDynamic2023.xlsx
+++ b/public/downloads/JiangDynamic2023.xlsx
@@ -1554,16 +1554,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.09641456870488674</v>
+        <v>0.0003285119445308737</v>
       </c>
       <c r="O3" s="5">
         <v>90</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6239493167297497</v>
+        <v>0.6148758494007502</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5864634383686206</v>
+        <v>0.577355914817737</v>
       </c>
       <c r="R3" s="5">
         <v>90</v>
@@ -1613,13 +1613,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.25612791588037</v>
+        <v>-0.2120207148619784</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2133333703906525</v>
+        <v>0.2084325702774979</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1885135138791156</v>
@@ -1795,22 +1795,22 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0495352906921368</v>
+        <v>0.2018627469725516</v>
       </c>
       <c r="O3" s="5">
         <v>87</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7508858906588549</v>
+        <v>0.7242529026652644</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.77806606575437</v>
+        <v>0.7399039568260343</v>
       </c>
       <c r="R3" s="5">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2034,16 +2034,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2804145229426144</v>
+        <v>0.1857621705389647</v>
       </c>
       <c r="O3" s="5">
         <v>89</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4618062706812343</v>
+        <v>0.4586604068967074</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4240305105108392</v>
+        <v>0.4204604853171626</v>
       </c>
       <c r="R3" s="5">
         <v>89</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.002603129700034401</v>
+        <v>0.01119119625514031</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1197182623623168</v>
+        <v>0.1194388860706113</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1067088039072779</v>
+        <v>0.1046702148347123</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02145297005440796</v>
+        <v>0.008932707612075319</v>
       </c>
       <c r="O3" s="5">
         <v>93</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4576975298520651</v>
+        <v>0.457793607074173</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4244395626137615</v>
+        <v>0.4242746515873984</v>
       </c>
       <c r="R3" s="5">
         <v>93</v>
@@ -2334,16 +2334,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1408404613225035</v>
+        <v>0.1278003310009126</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.273448582497741</v>
+        <v>0.2719996791286753</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2600475764835832</v>
+        <v>0.2581847007233559</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1731566757425481</v>
+        <v>0.1220997276312801</v>
       </c>
       <c r="O3" s="5">
         <v>92</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3008560352081979</v>
+        <v>0.3000208027965662</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2559832763496457</v>
+        <v>0.252944838722484</v>
       </c>
       <c r="R3" s="5">
         <v>92</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06516114618796109</v>
+        <v>-0.07253395663576612</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1434413483784359</v>
+        <v>0.1409837448958342</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1372867367827309</v>
+        <v>0.1362334781473302</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2588246301165238</v>
+        <v>0.1906809950061188</v>
       </c>
       <c r="O3" s="5">
         <v>92</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4678102639766296</v>
+        <v>0.4661118728896317</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.431773468123428</v>
+        <v>0.4306496217682499</v>
       </c>
       <c r="R3" s="5">
         <v>92</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2525062422311391</v>
+        <v>-0.1871188794262935</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1566734708037186</v>
+        <v>0.1611863535590222</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1586870681293875</v>
+        <v>0.1458072422991076</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -2998,22 +2998,22 @@
         <v>17</v>
       </c>
       <c r="N3" s="4">
-        <v>1.581612773675094</v>
+        <v>1.365806658590671</v>
       </c>
       <c r="O3" s="5">
         <v>47</v>
       </c>
       <c r="P3" s="4">
-        <v>1.190499194664065</v>
+        <v>1.191118232165884</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.9333839077604529</v>
+        <v>0.8866099038280335</v>
       </c>
       <c r="R3" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3237,16 +3237,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8566518384203367</v>
+        <v>-0.8148256323169023</v>
       </c>
       <c r="O3" s="5">
         <v>94</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2190812034743391</v>
+        <v>0.2168243242409684</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2271993236472406</v>
+        <v>0.2255717636664175</v>
       </c>
       <c r="R3" s="5">
         <v>94</v>
@@ -3296,16 +3296,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.07904438335567322</v>
+        <v>-0.02234425395784001</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1426137115841984</v>
+        <v>0.1363136972066614</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1038619601589447</v>
+        <v>0.09576194167353995</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -3711,16 +3711,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3343484532302963</v>
+        <v>-0.4185545975706759</v>
       </c>
       <c r="O3" s="5">
         <v>90</v>
       </c>
       <c r="P3" s="4">
-        <v>0.339901245954752</v>
+        <v>0.3329737297702391</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3142222757335684</v>
+        <v>0.3052173781115387</v>
       </c>
       <c r="R3" s="5">
         <v>90</v>
@@ -3770,16 +3770,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06280850348866807</v>
+        <v>-0.02606611033445461</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1386856787222541</v>
+        <v>0.1427681668505001</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1557907775687519</v>
+        <v>0.1505418642610071</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -3916,13 +3916,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4042101802733519</v>
+        <v>0.4028582156470541</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3833863798958821</v>
+        <v>0.3814148983504924</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3729603204355827</v>
+        <v>0.355272667990031</v>
       </c>
       <c r="K3" s="4">
         <v>90.79535573627912</v>
@@ -3948,13 +3948,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>88.72180451127819</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="C4" s="3">
         <v>4.511278195488721</v>
       </c>
       <c r="D4" s="3">
-        <v>6.766917293233083</v>
+        <v>6.015037593984962</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -3963,16 +3963,16 @@
         <v>3.759398496240602</v>
       </c>
       <c r="G4" s="3">
-        <v>3.007518796992481</v>
+        <v>2.255639097744361</v>
       </c>
       <c r="H4" s="4">
-        <v>0.749943831956182</v>
+        <v>0.7454150447180168</v>
       </c>
       <c r="I4" s="4">
-        <v>0.6989533938624787</v>
+        <v>0.7057183535132586</v>
       </c>
       <c r="J4" s="4">
-        <v>0.5427157389213658</v>
+        <v>0.5226462776231131</v>
       </c>
       <c r="K4" s="4">
         <v>90.80865428878319</v>
@@ -4016,13 +4016,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.3127307007823732</v>
+        <v>0.3051637869943561</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2957289045704428</v>
+        <v>0.2866935028479412</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3093916503042597</v>
+        <v>0.2576267391364383</v>
       </c>
       <c r="K5" s="4">
         <v>91.27103472968135</v>
@@ -4066,13 +4066,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4681317802741446</v>
+        <v>0.4559122515389293</v>
       </c>
       <c r="I6" s="4">
-        <v>0.4592244801517469</v>
+        <v>0.4507522009784881</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3863580490467429</v>
+        <v>0.429765454654706</v>
       </c>
       <c r="K6" s="4">
         <v>90.59485448314666</v>
@@ -4116,13 +4116,13 @@
         <v>1.503759398496241</v>
       </c>
       <c r="H7" s="4">
-        <v>0.2943241539491034</v>
+        <v>0.293704223873415</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2368639299572834</v>
+        <v>0.2356644872810048</v>
       </c>
       <c r="J7" s="4">
-        <v>0.4012331824952504</v>
+        <v>0.3993171122549586</v>
       </c>
       <c r="K7" s="4">
         <v>93.46324996163848</v>
@@ -4166,13 +4166,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.6065001410258234</v>
+        <v>0.5946275193342969</v>
       </c>
       <c r="I8" s="4">
-        <v>0.5760590307522571</v>
+        <v>0.5659433689352121</v>
       </c>
       <c r="J8" s="4">
-        <v>0.4290191597718513</v>
+        <v>0.4745368994240572</v>
       </c>
       <c r="K8" s="4">
         <v>91.15083627435936</v>
@@ -4198,13 +4198,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>81.95488721804512</v>
+        <v>80.45112781954887</v>
       </c>
       <c r="C9" s="3">
         <v>4.511278195488721</v>
       </c>
       <c r="D9" s="3">
-        <v>13.53383458646617</v>
+        <v>15.03759398496241</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -4213,16 +4213,16 @@
         <v>13.53383458646617</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>1.503759398496241</v>
       </c>
       <c r="H9" s="4">
-        <v>0.7297493373032723</v>
+        <v>0.7020841752775939</v>
       </c>
       <c r="I9" s="4">
-        <v>0.7644717432827777</v>
+        <v>0.7181624828949775</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4876513561060258</v>
+        <v>0.5777013253669302</v>
       </c>
       <c r="K9" s="4">
         <v>90.20663904659611</v>
@@ -4266,13 +4266,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4068171247342299</v>
+        <v>0.4021982966990882</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3775117915952573</v>
+        <v>0.3721434287351802</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3716209371465818</v>
+        <v>0.322604889198743</v>
       </c>
       <c r="K10" s="4">
         <v>91.04700526827273</v>
@@ -4316,13 +4316,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.4542013147619492</v>
+        <v>0.453976497055672</v>
       </c>
       <c r="I11" s="4">
-        <v>0.4274139239694594</v>
+        <v>0.4270724562006362</v>
       </c>
       <c r="J11" s="4">
-        <v>0.3536619496173149</v>
+        <v>0.3479656031139638</v>
       </c>
       <c r="K11" s="4">
         <v>91.87765331696588</v>
@@ -4366,13 +4366,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2810251674914412</v>
+        <v>0.2776725551002562</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2476260997260189</v>
+        <v>0.2424922504206411</v>
       </c>
       <c r="J12" s="4">
-        <v>0.3450093379721784</v>
+        <v>0.3221850557495607</v>
       </c>
       <c r="K12" s="4">
         <v>93.56963838166847</v>
@@ -4416,13 +4416,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.4170568556693248</v>
+        <v>0.4143786786333284</v>
       </c>
       <c r="I13" s="4">
-        <v>0.3890062357698064</v>
+        <v>0.385515997134083</v>
       </c>
       <c r="J13" s="4">
-        <v>0.3622978995901615</v>
+        <v>0.3258429637326886</v>
       </c>
       <c r="K13" s="4">
         <v>92.25180297682985</v>
@@ -4448,13 +4448,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="3">
-        <v>39.09090909090909</v>
+        <v>38.18181818181819</v>
       </c>
       <c r="C14" s="3">
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>60.90909090909091</v>
+        <v>61.81818181818181</v>
       </c>
       <c r="E14" s="3">
         <v>4.545454545454546</v>
@@ -4463,16 +4463,16 @@
         <v>51.81818181818182</v>
       </c>
       <c r="G14" s="3">
-        <v>4.545454545454546</v>
+        <v>5.454545454545454</v>
       </c>
       <c r="H14" s="4">
-        <v>1.144105563593081</v>
+        <v>1.144673952572024</v>
       </c>
       <c r="I14" s="4">
-        <v>0.9145739170096057</v>
+        <v>0.8684657229148427</v>
       </c>
       <c r="J14" s="4">
-        <v>0.856047107888858</v>
+        <v>0.7586244436917163</v>
       </c>
       <c r="K14" s="4">
         <v>76.87786023500307</v>
@@ -4516,13 +4516,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2128247723196913</v>
+        <v>0.2102370911199796</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2186511895440913</v>
+        <v>0.2165750433302776</v>
       </c>
       <c r="J15" s="4">
-        <v>0.3949315992231434</v>
+        <v>0.4164867798392097</v>
       </c>
       <c r="K15" s="4">
         <v>93.41280148423051</v>
@@ -4616,13 +4616,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.3234381540902749</v>
+        <v>0.3174114564404423</v>
       </c>
       <c r="I17" s="4">
-        <v>0.3027890748350765</v>
+        <v>0.2940552276274797</v>
       </c>
       <c r="J17" s="4">
-        <v>0.3492609618536484</v>
+        <v>0.2926216779340788</v>
       </c>
       <c r="K17" s="4">
         <v>92.5754483611631</v>
@@ -5549,13 +5549,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C4" s="5">
         <v>6</v>
       </c>
       <c r="D4" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="5">
         <v>0</v>
@@ -5564,7 +5564,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -5769,13 +5769,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C9" s="5">
         <v>6</v>
       </c>
       <c r="D9" s="5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E9" s="5">
         <v>0</v>
@@ -5784,7 +5784,7 @@
         <v>18</v>
       </c>
       <c r="G9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="5">
         <v>0</v>
@@ -5989,13 +5989,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
       </c>
       <c r="D14" s="5">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" s="5">
         <v>5</v>
@@ -6004,7 +6004,7 @@
         <v>57</v>
       </c>
       <c r="G14" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="5">
         <v>5</v>
@@ -6319,16 +6319,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.08247222784529971</v>
+        <v>0.04262232326902904</v>
       </c>
       <c r="O3" s="5">
         <v>92</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4335050162872681</v>
+        <v>0.4326741536574558</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4191752189883338</v>
+        <v>0.417638706272302</v>
       </c>
       <c r="R3" s="5">
         <v>92</v>
@@ -6378,16 +6378,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7249473826592066</v>
+        <v>-0.691986683129926</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1228267362154257</v>
+        <v>0.1184322141842939</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1018654030620746</v>
+        <v>0.09527326315621849</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -6560,22 +6560,22 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>0.08358244615315355</v>
+        <v>-0.003074152812359898</v>
       </c>
       <c r="O3" s="5">
         <v>94</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8315361465461627</v>
+        <v>0.8290801787489189</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7547966148785786</v>
+        <v>0.7663953016402867</v>
       </c>
       <c r="R3" s="5">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -6619,16 +6619,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1034192243750264</v>
+        <v>-0.04824373414061256</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2369869917534844</v>
+        <v>0.2223383625781392</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2419385551562654</v>
+        <v>0.2279626842708543</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -6801,16 +6801,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2864326960377471</v>
+        <v>0.184221669294061</v>
       </c>
       <c r="O3" s="5">
         <v>95</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3299861176413893</v>
+        <v>0.3226029423375518</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.309983392113737</v>
+        <v>0.2999820999118954</v>
       </c>
       <c r="R3" s="5">
         <v>95</v>
@@ -6860,16 +6860,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1520537010616831</v>
+        <v>0.1451433534733724</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2484736946983138</v>
+        <v>0.2461702455022103</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2493712994703494</v>
+        <v>0.2483841069577336</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -7042,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.0752868972970023</v>
+        <v>0.1673938118151455</v>
       </c>
       <c r="O3" s="5">
         <v>88</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4998817478323011</v>
+        <v>0.4922524171448776</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4880947693974953</v>
+        <v>0.4821179070241289</v>
       </c>
       <c r="R3" s="5">
         <v>88</v>
@@ -7101,16 +7101,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02873115386428253</v>
+        <v>0.07254141302985317</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3176934193038707</v>
+        <v>0.306440911871189</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2727969549847694</v>
+        <v>0.2525424416059422</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.08040037005859409</v>
+        <v>0.07654362188594632</v>
       </c>
       <c r="O3" s="5">
         <v>94</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2737612898095583</v>
+        <v>0.2737687554045251</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.24308175578526</v>
+        <v>0.2430487480929089</v>
       </c>
       <c r="R3" s="5">
         <v>94</v>
@@ -7342,16 +7342,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.09018686809444887</v>
+        <v>0.1144195448974301</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.133287598753916</v>
+        <v>0.1342254082063555</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1250064900930603</v>
+        <v>0.1230324411266821</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
